--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="79">
   <si>
     <t>UID</t>
   </si>
@@ -88,6 +88,9 @@
     <t>2026-03-13</t>
   </si>
   <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
     <t>19:42:47</t>
   </si>
   <si>
@@ -160,6 +163,15 @@
     <t>16:40:10</t>
   </si>
   <si>
+    <t>21:54:19</t>
+  </si>
+  <si>
+    <t>21:55:43</t>
+  </si>
+  <si>
+    <t>22:22:26</t>
+  </si>
+  <si>
     <t>19:42:51</t>
   </si>
   <si>
@@ -227,6 +239,15 @@
   </si>
   <si>
     <t>16:40:06</t>
+  </si>
+  <si>
+    <t>21:54:15</t>
+  </si>
+  <si>
+    <t>21:54:26</t>
+  </si>
+  <si>
+    <t>22:08:52</t>
   </si>
   <si>
     <t>Auto Entry</t>
@@ -587,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -630,16 +651,16 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>0.07000000000000001</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -656,16 +677,16 @@
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>0.03</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -682,16 +703,16 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>0.03</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -708,16 +729,16 @@
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>0.13</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -734,16 +755,16 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>178.77</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -760,16 +781,16 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>0.05</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -786,16 +807,16 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>0.05</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -812,16 +833,16 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>0.95</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -838,16 +859,16 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>2.15</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -864,16 +885,16 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>0.05</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -890,16 +911,16 @@
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>0.1</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -916,16 +937,16 @@
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>0.08</v>
       </c>
       <c r="H13" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -942,16 +963,16 @@
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>0.17</v>
       </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -968,16 +989,16 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>0.22</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -994,16 +1015,16 @@
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>0.1</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1020,16 +1041,16 @@
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>0.12</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1046,16 +1067,16 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G18">
         <v>-1387.9</v>
       </c>
       <c r="H18" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1072,16 +1093,16 @@
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G19">
         <v>-441.63</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1098,16 +1119,16 @@
         <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G20">
         <v>0.4</v>
       </c>
       <c r="H20" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1124,16 +1145,16 @@
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G21">
         <v>918.85</v>
       </c>
       <c r="H21" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1150,16 +1171,16 @@
         <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G22">
         <v>22</v>
       </c>
       <c r="H22" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1176,16 +1197,16 @@
         <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G23">
         <v>0.1</v>
       </c>
       <c r="H23" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1202,16 +1223,16 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G24">
         <v>1.12</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1228,13 +1249,91 @@
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="F25" t="s">
+        <v>75</v>
       </c>
       <c r="G25">
+        <v>314.08</v>
+      </c>
+      <c r="H25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26">
+        <v>0.12</v>
+      </c>
+      <c r="H26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27">
+        <v>13.16</v>
+      </c>
+      <c r="H27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28">
         <v>0</v>
       </c>
-      <c r="H25" t="s">
-        <v>71</v>
+      <c r="H28" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="83">
   <si>
     <t>UID</t>
   </si>
@@ -91,6 +91,9 @@
     <t>2026-03-24</t>
   </si>
   <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
     <t>19:42:47</t>
   </si>
   <si>
@@ -172,6 +175,9 @@
     <t>22:22:26</t>
   </si>
   <si>
+    <t>18:06:58</t>
+  </si>
+  <si>
     <t>19:42:51</t>
   </si>
   <si>
@@ -248,6 +254,12 @@
   </si>
   <si>
     <t>22:08:52</t>
+  </si>
+  <si>
+    <t>18:06:51</t>
+  </si>
+  <si>
+    <t>18:17:13</t>
   </si>
   <si>
     <t>Auto Entry</t>
@@ -608,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -651,16 +663,16 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>0.07000000000000001</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -677,16 +689,16 @@
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>0.03</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -703,16 +715,16 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>0.03</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -729,16 +741,16 @@
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>0.13</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -755,16 +767,16 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>178.77</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -781,16 +793,16 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>0.05</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -807,16 +819,16 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>0.05</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -833,16 +845,16 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>0.95</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -859,16 +871,16 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>2.15</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -885,16 +897,16 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>0.05</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -911,16 +923,16 @@
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>0.1</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -937,16 +949,16 @@
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>0.08</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -963,16 +975,16 @@
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>0.17</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -989,16 +1001,16 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>0.22</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1015,16 +1027,16 @@
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G16">
         <v>0.1</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1041,16 +1053,16 @@
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17">
         <v>0.12</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1067,16 +1079,16 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G18">
         <v>-1387.9</v>
       </c>
       <c r="H18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1093,16 +1105,16 @@
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G19">
         <v>-441.63</v>
       </c>
       <c r="H19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1119,16 +1131,16 @@
         <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G20">
         <v>0.4</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1145,16 +1157,16 @@
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G21">
         <v>918.85</v>
       </c>
       <c r="H21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1171,16 +1183,16 @@
         <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G22">
         <v>22</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1197,16 +1209,16 @@
         <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G23">
         <v>0.1</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1223,16 +1235,16 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24">
         <v>1.12</v>
       </c>
       <c r="H24" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1249,16 +1261,16 @@
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G25">
         <v>314.08</v>
       </c>
       <c r="H25" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1275,16 +1287,16 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G26">
         <v>0.12</v>
       </c>
       <c r="H26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1301,16 +1313,16 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27">
         <v>13.16</v>
       </c>
       <c r="H27" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1327,13 +1339,42 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="F28" t="s">
+        <v>80</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>21344.42</v>
       </c>
       <c r="H28" t="s">
-        <v>78</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29">
+        <v>10.25</v>
+      </c>
+      <c r="H29" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
